--- a/Result/profitability/4538.xlsx
+++ b/Result/profitability/4538.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM52"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12375</v>
+        <v>0.09375000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>15.815</v>
+        <v>15.2075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30375</v>
+        <v>0.35375</v>
       </c>
       <c r="N3" t="n">
-        <v>15.9025</v>
+        <v>16.67</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -7036,6 +7036,135 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>102</v>
+      </c>
+      <c r="D53" t="n">
+        <v>86</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5.44%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.06875000000000001</v>
+      </c>
+      <c r="N53" t="n">
+        <v>15.925</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-0.4299999999999997</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-0.02602905569007263</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>-3.690000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>-0.186552072800809</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
